--- a/public/documents/requirement5/5_3/5_3_modelo_responsabilidades.xlsx
+++ b/public/documents/requirement5/5_3/5_3_modelo_responsabilidades.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thiff\integra-sgi\integra-sgi\public\documents\requirement5\5_3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FF99AECD-9A16-4F72-B852-5E052B32B0AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A842A571-D407-4863-9597-FB2FE43FEEA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{6D3D7074-1E79-4C40-A33A-B6E7367F1D78}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{6D3D7074-1E79-4C40-A33A-B6E7367F1D78}"/>
   </bookViews>
   <sheets>
-    <sheet name="Folha1" sheetId="1" r:id="rId1"/>
+    <sheet name="Matriz" sheetId="1" r:id="rId1"/>
+    <sheet name="Legenda" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="61">
   <si>
     <t>A Gestão de Topo assegura a disponibilização dos recursos necessários e atribui as responsabilidades e autoridades adequadas para:</t>
   </si>
@@ -126,9 +127,6 @@
   </si>
   <si>
     <t>—</t>
-  </si>
-  <si>
-    <t>Especificadades (ISO 9001 - 5.3)</t>
   </si>
   <si>
     <t>comunicadas e compreendidas por todos os colaboradores, garantindo o cumprimento dos requisitos das normas NP EN ISO 9001:2015, NP EN ISO 14001:2015 e NP ISO 45001:2023.</t>
@@ -262,12 +260,66 @@
   <si>
     <t xml:space="preserve">MATRIZ DE RESPONSABILIDADES E COMPETÊNCIAS </t>
   </si>
+  <si>
+    <t>Especificadades</t>
+  </si>
+  <si>
+    <t>Coluna</t>
+  </si>
+  <si>
+    <t>O que significa</t>
+  </si>
+  <si>
+    <t>Como preencher</t>
+  </si>
+  <si>
+    <t>Exemplos práticos</t>
+  </si>
+  <si>
+    <t>Função ou posição dentro da organização.</t>
+  </si>
+  <si>
+    <t>Indique o nome do cargo conforme organograma ou descrição de funções.</t>
+  </si>
+  <si>
+    <t>Operador de Produção; Técnico de Qualidade; Gestor Ambiental; Responsável de SST; Diretor Industrial</t>
+  </si>
+  <si>
+    <t>Conhecimentos, habilidades e formações necessárias para desempenhar o cargo.</t>
+  </si>
+  <si>
+    <t>Liste competências técnicas, comportamentais e requisitos legais (formações obrigatórias).</t>
+  </si>
+  <si>
+    <t>Formação em Segurança; Conhecimento em ISO 9001; Curso de Operação de Equipamentos; Capacidade de análise crítica</t>
+  </si>
+  <si>
+    <t>Obrigações relacionadas ao Sistema Integrado de Gestão (Qualidade, Ambiente e SST).</t>
+  </si>
+  <si>
+    <t>Descreva o que o cargo deve garantir, controlar, executar ou reportar dentro do SIG.</t>
+  </si>
+  <si>
+    <t>Cumprir procedimentos; Registar não conformidades; Garantir uso correto de EPIs; Monitorizar indicadores ambientais</t>
+  </si>
+  <si>
+    <t>Poder de decisão e nível de autonomia do cargo dentro do SIG.</t>
+  </si>
+  <si>
+    <t>Indique o que o cargo pode aprovar, rejeitar, solicitar ou interromper.</t>
+  </si>
+  <si>
+    <t>Autoridade para parar produção insegura; Aprovar documentos; Solicitar ações corretivas; Validar inspeções</t>
+  </si>
+  <si>
+    <t>LEGENDAS</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -298,6 +350,13 @@
     <font>
       <b/>
       <sz val="22"/>
+      <color theme="0"/>
+      <name val="Cambria"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
       <color theme="0"/>
       <name val="Cambria"/>
       <family val="1"/>
@@ -359,7 +418,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -371,10 +430,13 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -385,8 +447,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF203E5E"/>
       <color rgb="FF0F7343"/>
-      <color rgb="FF203E5E"/>
     </mruColors>
   </colors>
   <extLst>
@@ -405,15 +467,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>91440</xdr:colOff>
+      <xdr:colOff>114300</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>731520</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>73116</xdr:rowOff>
+      <xdr:colOff>754380</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>4536</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -443,7 +505,63 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="91440" y="0"/>
+          <a:off x="114300" y="7620"/>
+          <a:ext cx="769620" cy="751296"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>647700</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>12156</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagem 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7CB1BEA8-0F66-464E-A96E-9F8C9D59A264}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect l="10345" t="10837" r="6897" b="8375"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="76200" y="0"/>
           <a:ext cx="769620" cy="751296"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -790,7 +908,7 @@
     <row r="1" spans="2:7" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:7" ht="47.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
@@ -801,23 +919,23 @@
     <row r="3" spans="2:7" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="2:7" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="2:7" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -831,49 +949,49 @@
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B15" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17" spans="2:6" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="18" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B18" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20" spans="2:6" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="21" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B21" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B22" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="23" spans="2:6" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -891,7 +1009,7 @@
         <v>4</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25" spans="2:6" ht="27.6" x14ac:dyDescent="0.25">
@@ -987,4 +1105,104 @@
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB1D8E3A-EE21-4B7F-B90E-FA847B0A456D}">
+  <dimension ref="B2:E8"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="2.88671875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22.109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="29.21875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="30" style="1" customWidth="1"/>
+    <col min="5" max="5" width="34.44140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.88671875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:5" ht="44.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+    </row>
+    <row r="4" spans="2:5" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" ht="55.2" x14ac:dyDescent="0.25">
+      <c r="B5" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" ht="69" x14ac:dyDescent="0.25">
+      <c r="B6" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" ht="69" x14ac:dyDescent="0.25">
+      <c r="B7" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" ht="55.2" x14ac:dyDescent="0.25">
+      <c r="B8" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:E2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/public/documents/requirement5/5_3/5_3_modelo_responsabilidades.xlsx
+++ b/public/documents/requirement5/5_3/5_3_modelo_responsabilidades.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thiff\integra-sgi\integra-sgi\public\documents\requirement5\5_3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A842A571-D407-4863-9597-FB2FE43FEEA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BC22005-1CB2-4CB7-91C6-320CCB93FB60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{6D3D7074-1E79-4C40-A33A-B6E7367F1D78}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="2" xr2:uid="{6D3D7074-1E79-4C40-A33A-B6E7367F1D78}"/>
   </bookViews>
   <sheets>
     <sheet name="Matriz" sheetId="1" r:id="rId1"/>
     <sheet name="Legenda" sheetId="2" r:id="rId2"/>
+    <sheet name="Como Preencher" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="78">
   <si>
     <t>A Gestão de Topo assegura a disponibilização dos recursos necessários e atribui as responsabilidades e autoridades adequadas para:</t>
   </si>
@@ -314,12 +315,63 @@
   <si>
     <t>LEGENDAS</t>
   </si>
+  <si>
+    <t>Campo</t>
+  </si>
+  <si>
+    <t>Exemplo</t>
+  </si>
+  <si>
+    <t>Indique o nome do cargo ou função existente na organização.</t>
+  </si>
+  <si>
+    <t>Gestor SIG, Diretor Geral, Supervisor de Produção, Técnico de Qualidade</t>
+  </si>
+  <si>
+    <t>Descreva os conhecimentos, aptidões ou qualificações necessárias para exercer a função. Utilize palavras-chave ou pequenas descrições.</t>
+  </si>
+  <si>
+    <t>Liderança estratégica, Auditorias internas, Gestão ambiental, Operação de equipamentos</t>
+  </si>
+  <si>
+    <t>Descreva as principais responsabilidades da função relacionadas com o Sistema de Gestão Integrado. Utilize verbos no infinitivo.</t>
+  </si>
+  <si>
+    <t>Coordenar auditorias, Aprovar políticas, Monitorizar indicadores, Controlar processos</t>
+  </si>
+  <si>
+    <t>Indique o nível de decisão que a função possui dentro da organização. Pode ser utilizado um critério como Máxima, Alta, Média, Baixa ou Operacional, conforme a estrutura da empresa.</t>
+  </si>
+  <si>
+    <t>Especificidades</t>
+  </si>
+  <si>
+    <t>Indique as responsabilidades específicas da função utilizando a legenda definida neste documento (a, b, c, d, e, etc.). Caso não existam responsabilidades específicas, pode utilizar "—".</t>
+  </si>
+  <si>
+    <t>a, b, d</t>
+  </si>
+  <si>
+    <t>COMO PREENCHER</t>
+  </si>
+  <si>
+    <t>Cada linha da matriz deve corresponder a um cargo ou função existente na empresa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Matriz de Responsabilidades e Competências tem como objetivo definir, de forma clara, quais são as funções existentes na organização, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">as competências necessárias para cada cargo, as suas responsabilidades no Sistema de Gestão Integrado (SIG), </t>
+  </si>
+  <si>
+    <t>o nível de autoridade e a relação com as responsabilidades definidas pela organização.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -357,6 +409,13 @@
     <font>
       <b/>
       <sz val="24"/>
+      <color theme="0"/>
+      <name val="Cambria"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
       <color theme="0"/>
       <name val="Cambria"/>
       <family val="1"/>
@@ -418,7 +477,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -430,14 +489,20 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -447,8 +512,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF0F7343"/>
       <color rgb="FF203E5E"/>
-      <color rgb="FF0F7343"/>
     </mruColors>
   </colors>
   <extLst>
@@ -563,6 +628,62 @@
         <a:xfrm>
           <a:off x="76200" y="0"/>
           <a:ext cx="769620" cy="751296"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>15239</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>777240</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>48622</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagem 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ED782C51-F49A-4CD5-9B48-886AF186617F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect l="10345" t="10837" r="6897" b="8375"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="38100" y="15239"/>
+          <a:ext cx="838200" cy="818243"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -907,14 +1028,14 @@
   <sheetData>
     <row r="1" spans="2:7" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:7" ht="47.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="7"/>
     </row>
     <row r="3" spans="2:7" ht="6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
@@ -1121,12 +1242,12 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:5" ht="44.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
     </row>
     <row r="4" spans="2:5" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
@@ -1156,7 +1277,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="2:5" ht="69" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:5" ht="55.2" x14ac:dyDescent="0.25">
       <c r="B6" s="4" t="s">
         <v>2</v>
       </c>
@@ -1170,7 +1291,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="7" spans="2:5" ht="69" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:5" ht="55.2" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
         <v>3</v>
       </c>
@@ -1205,4 +1326,121 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6F249B9-625E-4599-9599-880CB680EE4F}">
+  <dimension ref="B1:D15"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="1.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.44140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="48.88671875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="42.33203125" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="8.88671875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:4" ht="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:4" ht="55.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+    </row>
+    <row r="3" spans="2:4" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B4" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B5" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B6" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B8" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" ht="7.2" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="2:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="B11" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="B12" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="B13" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4" ht="55.2" x14ac:dyDescent="0.25">
+      <c r="B14" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4" ht="55.2" x14ac:dyDescent="0.25">
+      <c r="B15" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>72</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>